--- a/downloads/24.08.2026 to 30.08.2026.xlsx
+++ b/downloads/24.08.2026 to 30.08.2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sadashiv.bhimanna\Desktop\2026-27\Second Year Time Table\Weekly time table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FD8630F-1EEA-4087-BA28-05812438A3EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E96B39CD-6321-48F1-B6A7-7ED689C6EF25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="49">
   <si>
     <t>Day/
 Time</t>
@@ -264,6 +264,12 @@
 Rescheduled class
 L06, 2nd floor
 Prof Krishna</t>
+  </si>
+  <si>
+    <t>Pricing Strategy
+Rescheduled class
+L06, 2nd floor
+Dr Srividya Raghavan</t>
   </si>
 </sst>
 </file>
@@ -903,7 +909,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -933,9 +939,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1095,9 +1098,6 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1187,6 +1187,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1514,18 +1517,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="100" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
     </row>
     <row r="2" spans="1:10" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -1546,290 +1549,289 @@
       <c r="F2" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G2" s="105" t="s">
+      <c r="G2" s="104" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="106"/>
-      <c r="I2" s="30" t="s">
+      <c r="H2" s="105"/>
+      <c r="I2" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="J2" s="43" t="s">
+      <c r="J2" s="42" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="107" t="s">
+      <c r="A3" s="106" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="56" t="s">
         <v>14</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="108" t="s">
+      <c r="E3" s="107" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="82" t="s">
+      <c r="F3" s="80" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="83"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="66" t="s">
+      <c r="G3" s="81"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="65" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="40"/>
+      <c r="J3" s="39"/>
     </row>
     <row r="4" spans="1:10" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="104"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="84"/>
-      <c r="D4" s="100" t="s">
+      <c r="A4" s="103"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="109"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="67" t="s">
+      <c r="E4" s="108"/>
+      <c r="F4" s="99" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="64"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="37"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="36"/>
     </row>
-    <row r="5" spans="1:10" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="104" t="s">
+    <row r="5" spans="1:10" ht="62.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="103" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="60" t="s">
+      <c r="B5" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="61" t="s">
+      <c r="C5" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="62" t="s">
+      <c r="D5" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="109"/>
-      <c r="F5" s="58" t="s">
+      <c r="E5" s="108"/>
+      <c r="F5" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="65" t="s">
+      <c r="G5" s="64" t="s">
         <v>19</v>
       </c>
       <c r="H5" s="9"/>
-      <c r="I5" s="32"/>
-      <c r="J5" s="37"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="36"/>
     </row>
     <row r="6" spans="1:10" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="104"/>
-      <c r="B6" s="49"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="109"/>
-      <c r="F6" s="24" t="s">
+      <c r="A6" s="103"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="11"/>
+      <c r="E6" s="108"/>
+      <c r="F6" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="47" t="s">
+      <c r="G6" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="13"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="37"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="32"/>
+      <c r="J6" s="36"/>
     </row>
     <row r="7" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="104" t="s">
+      <c r="A7" s="103" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="44" t="s">
+      <c r="B7" s="13"/>
+      <c r="C7" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="68"/>
-      <c r="E7" s="109"/>
-      <c r="F7" s="15" t="s">
+      <c r="D7" s="66"/>
+      <c r="E7" s="108"/>
+      <c r="F7" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="46" t="s">
+      <c r="G7" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="H7" s="16" t="s">
+      <c r="H7" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="I7" s="34"/>
-      <c r="J7" s="37"/>
+      <c r="I7" s="33"/>
+      <c r="J7" s="36"/>
     </row>
     <row r="8" spans="1:10" ht="63.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="104"/>
+      <c r="A8" s="103"/>
       <c r="B8" s="10"/>
       <c r="C8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="109"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="19" t="s">
+      <c r="E8" s="108"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="18" t="s">
         <v>17</v>
       </c>
       <c r="H8" s="7"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="39"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="38"/>
     </row>
     <row r="9" spans="1:10" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="104" t="s">
+      <c r="A9" s="103" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="97"/>
-      <c r="C9" s="98"/>
-      <c r="D9" s="20" t="s">
+      <c r="B9" s="95"/>
+      <c r="C9" s="96"/>
+      <c r="D9" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="109"/>
-      <c r="F9" s="20" t="s">
+      <c r="E9" s="108"/>
+      <c r="F9" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="G9" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" s="35" t="s">
+      <c r="H9" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="I9" s="42" t="s">
+      <c r="I9" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="J9" s="73"/>
+      <c r="J9" s="71"/>
     </row>
     <row r="10" spans="1:10" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="104"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="69"/>
-      <c r="D10" s="45" t="s">
+      <c r="A10" s="103"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="67"/>
+      <c r="D10" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="109"/>
+      <c r="E10" s="108"/>
       <c r="F10" s="7"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="85"/>
-      <c r="J10" s="48"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="23"/>
+      <c r="I10" s="83"/>
+      <c r="J10" s="47"/>
     </row>
     <row r="11" spans="1:10" ht="63" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="103" t="s">
+      <c r="A11" s="102" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="53"/>
-      <c r="C11" s="50" t="s">
+      <c r="B11" s="52"/>
+      <c r="C11" s="49" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="23" t="s">
+      <c r="D11" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="109"/>
+      <c r="E11" s="108"/>
       <c r="F11" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="G11" s="82" t="s">
+      <c r="G11" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="H11" s="90"/>
-      <c r="I11" s="42" t="s">
+      <c r="H11" s="88"/>
+      <c r="I11" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="J11" s="40"/>
+      <c r="J11" s="39"/>
     </row>
     <row r="12" spans="1:10" ht="63.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="104"/>
-      <c r="B12" s="49"/>
-      <c r="C12" s="69" t="s">
+      <c r="A12" s="103"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="70" t="s">
+      <c r="D12" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="109"/>
-      <c r="F12" s="86"/>
-      <c r="G12" s="89"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="73"/>
-      <c r="J12" s="37"/>
+      <c r="E12" s="108"/>
+      <c r="F12" s="84"/>
+      <c r="G12" s="87"/>
+      <c r="H12" s="53"/>
+      <c r="I12" s="71"/>
+      <c r="J12" s="36"/>
     </row>
     <row r="13" spans="1:10" ht="63.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="55" t="s">
+      <c r="A13" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="78"/>
-      <c r="C13" s="71" t="s">
+      <c r="B13" s="76"/>
+      <c r="C13" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="71" t="s">
+      <c r="D13" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="56"/>
-      <c r="F13" s="87" t="s">
+      <c r="E13" s="55"/>
+      <c r="F13" s="85" t="s">
         <v>44</v>
       </c>
-      <c r="G13" s="88" t="s">
+      <c r="G13" s="86" t="s">
         <v>44</v>
       </c>
-      <c r="H13" s="77"/>
-      <c r="I13" s="74"/>
-      <c r="J13" s="37"/>
+      <c r="H13" s="75"/>
+      <c r="I13" s="72"/>
+      <c r="J13" s="36"/>
     </row>
     <row r="14" spans="1:10" ht="63.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="55"/>
-      <c r="B14" s="79"/>
-      <c r="C14" s="72" t="s">
+      <c r="A14" s="54"/>
+      <c r="B14" s="77"/>
+      <c r="C14" s="70" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="72" t="s">
+      <c r="D14" s="70" t="s">
         <v>41</v>
       </c>
-      <c r="E14" s="56"/>
-      <c r="F14" s="91"/>
-      <c r="G14" s="92"/>
-      <c r="H14" s="64"/>
-      <c r="I14" s="74"/>
-      <c r="J14" s="37"/>
+      <c r="E14" s="55"/>
+      <c r="F14" s="89"/>
+      <c r="G14" s="90"/>
+      <c r="H14" s="63"/>
+      <c r="I14" s="72"/>
+      <c r="J14" s="36"/>
     </row>
     <row r="15" spans="1:10" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="103" t="s">
+      <c r="A15" s="102" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="36"/>
-      <c r="C15" s="80" t="s">
+      <c r="B15" s="35"/>
+      <c r="C15" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="81" t="s">
+      <c r="D15" s="79" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="26"/>
-      <c r="F15" s="95" t="s">
+      <c r="E15" s="25"/>
+      <c r="F15" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="G15" s="96"/>
-      <c r="H15" s="93"/>
-      <c r="I15" s="51"/>
-      <c r="J15" s="37"/>
+      <c r="G15" s="94"/>
+      <c r="H15" s="91"/>
+      <c r="I15" s="50"/>
+      <c r="J15" s="36"/>
     </row>
     <row r="16" spans="1:10" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="104"/>
-      <c r="B16" s="27"/>
-      <c r="C16" s="75" t="s">
+      <c r="A16" s="103"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="76" t="s">
+      <c r="D16" s="74" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="28"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="94"/>
-      <c r="I16" s="52"/>
-      <c r="J16" s="38"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="92"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="9">

--- a/downloads/24.08.2026 to 30.08.2026.xlsx
+++ b/downloads/24.08.2026 to 30.08.2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sadashiv.bhimanna\Desktop\2026-27\Second Year Time Table\Weekly time table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E96B39CD-6321-48F1-B6A7-7ED689C6EF25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A24000A3-F6B6-49DD-A692-A362A17D0374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="49">
   <si>
     <t>Day/
 Time</t>
@@ -909,7 +909,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1097,9 +1097,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1517,18 +1514,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="99" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
-      <c r="J1" s="101"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
+      <c r="F1" s="100"/>
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
+      <c r="J1" s="100"/>
     </row>
     <row r="2" spans="1:10" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -1549,10 +1546,10 @@
       <c r="F2" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G2" s="104" t="s">
+      <c r="G2" s="103" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="105"/>
+      <c r="H2" s="104"/>
       <c r="I2" s="29" t="s">
         <v>32</v>
       </c>
@@ -1561,7 +1558,7 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="106" t="s">
+      <c r="A3" s="105" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="56" t="s">
@@ -1573,13 +1570,13 @@
       <c r="D3" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="107" t="s">
+      <c r="E3" s="106" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="80" t="s">
+      <c r="F3" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="81"/>
+      <c r="G3" s="80"/>
       <c r="H3" s="62"/>
       <c r="I3" s="65" t="s">
         <v>16</v>
@@ -1587,23 +1584,23 @@
       <c r="J3" s="39"/>
     </row>
     <row r="4" spans="1:10" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="103"/>
+      <c r="A4" s="102"/>
       <c r="B4" s="58"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="98" t="s">
+      <c r="C4" s="81"/>
+      <c r="D4" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="108"/>
-      <c r="F4" s="99" t="s">
+      <c r="E4" s="107"/>
+      <c r="F4" s="98" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="97"/>
+      <c r="G4" s="96"/>
       <c r="H4" s="63"/>
       <c r="I4" s="30"/>
       <c r="J4" s="36"/>
     </row>
     <row r="5" spans="1:10" ht="62.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="103" t="s">
+      <c r="A5" s="102" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="59" t="s">
@@ -1615,7 +1612,7 @@
       <c r="D5" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="108"/>
+      <c r="E5" s="107"/>
       <c r="F5" s="57" t="s">
         <v>11</v>
       </c>
@@ -1627,13 +1624,13 @@
       <c r="J5" s="36"/>
     </row>
     <row r="6" spans="1:10" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="103"/>
+      <c r="A6" s="102"/>
       <c r="B6" s="48"/>
       <c r="C6" s="20" t="s">
         <v>48</v>
       </c>
       <c r="D6" s="11"/>
-      <c r="E6" s="108"/>
+      <c r="E6" s="107"/>
       <c r="F6" s="23" t="s">
         <v>20</v>
       </c>
@@ -1645,15 +1642,17 @@
       <c r="J6" s="36"/>
     </row>
     <row r="7" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="103" t="s">
+      <c r="A7" s="102" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="66"/>
-      <c r="E7" s="108"/>
+      <c r="D7" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="107"/>
       <c r="F7" s="14" t="s">
         <v>25</v>
       </c>
@@ -1667,7 +1666,7 @@
       <c r="J7" s="36"/>
     </row>
     <row r="8" spans="1:10" ht="63.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="103"/>
+      <c r="A8" s="102"/>
       <c r="B8" s="10"/>
       <c r="C8" s="7" t="s">
         <v>22</v>
@@ -1675,7 +1674,7 @@
       <c r="D8" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="108"/>
+      <c r="E8" s="107"/>
       <c r="F8" s="17"/>
       <c r="G8" s="18" t="s">
         <v>17</v>
@@ -1685,15 +1684,15 @@
       <c r="J8" s="38"/>
     </row>
     <row r="9" spans="1:10" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="103" t="s">
+      <c r="A9" s="102" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="95"/>
-      <c r="C9" s="96"/>
+      <c r="B9" s="94"/>
+      <c r="C9" s="95"/>
       <c r="D9" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="108"/>
+      <c r="E9" s="107"/>
       <c r="F9" s="19" t="s">
         <v>25</v>
       </c>
@@ -1703,24 +1702,24 @@
       <c r="I9" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="J9" s="71"/>
+      <c r="J9" s="70"/>
     </row>
     <row r="10" spans="1:10" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="103"/>
+      <c r="A10" s="102"/>
       <c r="B10" s="21"/>
-      <c r="C10" s="67"/>
+      <c r="C10" s="66"/>
       <c r="D10" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="108"/>
+      <c r="E10" s="107"/>
       <c r="F10" s="7"/>
       <c r="G10" s="23"/>
       <c r="H10" s="23"/>
-      <c r="I10" s="83"/>
+      <c r="I10" s="82"/>
       <c r="J10" s="47"/>
     </row>
     <row r="11" spans="1:10" ht="63" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="102" t="s">
+      <c r="A11" s="101" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="52"/>
@@ -1730,106 +1729,106 @@
       <c r="D11" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="108"/>
+      <c r="E11" s="107"/>
       <c r="F11" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="G11" s="80" t="s">
+      <c r="G11" s="79" t="s">
         <v>46</v>
       </c>
-      <c r="H11" s="88"/>
+      <c r="H11" s="87"/>
       <c r="I11" s="41" t="s">
         <v>36</v>
       </c>
       <c r="J11" s="39"/>
     </row>
     <row r="12" spans="1:10" ht="63.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="103"/>
+      <c r="A12" s="102"/>
       <c r="B12" s="48"/>
-      <c r="C12" s="67" t="s">
+      <c r="C12" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="68" t="s">
+      <c r="D12" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="108"/>
-      <c r="F12" s="84"/>
-      <c r="G12" s="87"/>
+      <c r="E12" s="107"/>
+      <c r="F12" s="83"/>
+      <c r="G12" s="86"/>
       <c r="H12" s="53"/>
-      <c r="I12" s="71"/>
+      <c r="I12" s="70"/>
       <c r="J12" s="36"/>
     </row>
     <row r="13" spans="1:10" ht="63.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="76"/>
-      <c r="C13" s="69" t="s">
+      <c r="B13" s="75"/>
+      <c r="C13" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="69" t="s">
+      <c r="D13" s="68" t="s">
         <v>40</v>
       </c>
       <c r="E13" s="55"/>
-      <c r="F13" s="85" t="s">
+      <c r="F13" s="84" t="s">
         <v>44</v>
       </c>
-      <c r="G13" s="86" t="s">
+      <c r="G13" s="85" t="s">
         <v>44</v>
       </c>
-      <c r="H13" s="75"/>
-      <c r="I13" s="72"/>
+      <c r="H13" s="74"/>
+      <c r="I13" s="71"/>
       <c r="J13" s="36"/>
     </row>
     <row r="14" spans="1:10" ht="63.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="54"/>
-      <c r="B14" s="77"/>
-      <c r="C14" s="70" t="s">
+      <c r="B14" s="76"/>
+      <c r="C14" s="69" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="70" t="s">
+      <c r="D14" s="69" t="s">
         <v>41</v>
       </c>
       <c r="E14" s="55"/>
-      <c r="F14" s="89"/>
-      <c r="G14" s="90"/>
+      <c r="F14" s="88"/>
+      <c r="G14" s="89"/>
       <c r="H14" s="63"/>
-      <c r="I14" s="72"/>
+      <c r="I14" s="71"/>
       <c r="J14" s="36"/>
     </row>
     <row r="15" spans="1:10" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="102" t="s">
+      <c r="A15" s="101" t="s">
         <v>38</v>
       </c>
       <c r="B15" s="35"/>
-      <c r="C15" s="78" t="s">
+      <c r="C15" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="79" t="s">
+      <c r="D15" s="78" t="s">
         <v>30</v>
       </c>
       <c r="E15" s="25"/>
-      <c r="F15" s="93" t="s">
+      <c r="F15" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="G15" s="94"/>
-      <c r="H15" s="91"/>
+      <c r="G15" s="93"/>
+      <c r="H15" s="90"/>
       <c r="I15" s="50"/>
       <c r="J15" s="36"/>
     </row>
     <row r="16" spans="1:10" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="103"/>
+      <c r="A16" s="102"/>
       <c r="B16" s="26"/>
-      <c r="C16" s="73" t="s">
+      <c r="C16" s="72" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="74" t="s">
+      <c r="D16" s="73" t="s">
         <v>42</v>
       </c>
       <c r="E16" s="27"/>
       <c r="F16" s="17"/>
       <c r="G16" s="24"/>
-      <c r="H16" s="92"/>
+      <c r="H16" s="91"/>
       <c r="I16" s="51"/>
       <c r="J16" s="37"/>
     </row>
